--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136090687</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136090953</v>
+        <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>92539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Smällbäcksmossen, Smällbäcksmossen, Sm</t>
+          <t>Smällbäcksmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548164</v>
+        <v>548127</v>
       </c>
       <c r="R3" t="n">
-        <v>6253973</v>
+        <v>6253961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,27 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hörde den där punkten är satt.</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136090953</t>
+          <t>https://artportalen.se/Sighting/137193430</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135319478</v>
+        <v>136090953</v>
       </c>
       <c r="B4" t="n">
-        <v>98138</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547981</v>
+        <v>548164</v>
       </c>
       <c r="R4" t="n">
-        <v>6253982</v>
+        <v>6253973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +969,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hörde den där punkten är satt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +1014,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136090953</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135319478</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smällbäcksmossen, Smällbäcksmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547981</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6253982</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sandra Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135319478</t>
         </is>
@@ -1024,6 +1136,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18694-2024 artfynd.xlsx
+++ b/artfynd/A 18694-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137193430</v>
       </c>
       <c r="B3" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
